--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_0_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/6_five_bus_radial_grid_1ph_dd_MP_pf_sc_results_0_branch.xlsx
@@ -876,37 +876,37 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.04212936833768E-14</v>
+        <v>-2.605323420844191E-14</v>
       </c>
       <c r="O2">
-        <v>2.084254352028575E-14</v>
+        <v>-1.042133752563278E-14</v>
       </c>
       <c r="P2">
-        <v>-4.453689501968079E-20</v>
+        <v>5.210602297287542E-15</v>
       </c>
       <c r="Q2">
-        <v>6.264497858957098E-29</v>
+        <v>1.563194052506517E-14</v>
       </c>
       <c r="R2">
-        <v>-1.302614501295364E-14</v>
+        <v>1.3027089198387E-14</v>
       </c>
       <c r="S2">
-        <v>4.72786253231053E-19</v>
+        <v>4.727943969756028E-19</v>
       </c>
       <c r="T2">
-        <v>5.210646841688246E-15</v>
+        <v>5.210646841688062E-15</v>
       </c>
       <c r="U2">
-        <v>5.763397467220029E-09</v>
+        <v>5.763410493837126E-09</v>
       </c>
       <c r="V2">
-        <v>-5.763387050089315E-09</v>
+        <v>-5.763397471383004E-09</v>
       </c>
       <c r="W2">
-        <v>-5.210646841688372E-15</v>
+        <v>-5.210646841688187E-15</v>
       </c>
       <c r="X2">
-        <v>-5.763392256087288E-09</v>
+        <v>-5.763413098674642E-09</v>
       </c>
       <c r="Y2">
         <v>5.763397471868898E-09</v>
@@ -933,37 +933,37 @@
         <v>1.100000023808765</v>
       </c>
       <c r="AG2">
-        <v>0.5500000117057469</v>
+        <v>0.5500000117057466</v>
       </c>
       <c r="AH2">
-        <v>0.5500000121030187</v>
+        <v>0.5500000121030189</v>
       </c>
       <c r="AI2">
         <v>1.100000023808766</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000116593773</v>
+        <v>0.5500000116593772</v>
       </c>
       <c r="AK2">
         <v>0.5500000121493878</v>
       </c>
       <c r="AL2">
-        <v>6.817995222150363E-13</v>
+        <v>6.768911557736487E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999995569</v>
+        <v>-179.9999999995568</v>
       </c>
       <c r="AN2">
         <v>179.9999999995499</v>
       </c>
       <c r="AO2">
-        <v>6.888382555795436E-13</v>
+        <v>6.740444786081727E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999952996</v>
+        <v>-179.9999999952994</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999952926</v>
+        <v>179.9999999952925</v>
       </c>
     </row>
   </sheetData>
@@ -1148,40 +1148,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.605323420851882E-14</v>
+        <v>-1.04212936834075E-14</v>
       </c>
       <c r="O2">
-        <v>-7.307829259720459E-10</v>
+        <v>-7.307523446882842E-10</v>
       </c>
       <c r="P2">
-        <v>-2.039313734253751E-09</v>
+        <v>-2.039299493936973E-09</v>
       </c>
       <c r="Q2">
-        <v>1.563194052511122E-14</v>
+        <v>5.210646841703724E-15</v>
       </c>
       <c r="R2">
-        <v>7.307914380432017E-10</v>
+        <v>7.307650617072342E-10</v>
       </c>
       <c r="S2">
-        <v>2.039316238676205E-09</v>
+        <v>2.039289440021766E-09</v>
       </c>
       <c r="T2">
-        <v>-5.210646841704026E-15</v>
+        <v>-5.210646841703873E-15</v>
       </c>
       <c r="U2">
-        <v>5.822510467193816E-09</v>
+        <v>5.822508683328154E-09</v>
       </c>
       <c r="V2">
-        <v>-3.556075036161045E-09</v>
+        <v>-3.556075895985843E-09</v>
       </c>
       <c r="W2">
-        <v>1.04212936834077E-14</v>
+        <v>5.210646841703825E-15</v>
       </c>
       <c r="X2">
-        <v>-5.822504826306648E-09</v>
+        <v>-5.822518630393806E-09</v>
       </c>
       <c r="Y2">
-        <v>3.556069168397299E-09</v>
+        <v>3.556075074159447E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1208,19 +1208,19 @@
         <v>0.6816683458635714</v>
       </c>
       <c r="AH2">
-        <v>0.4761907155780347</v>
+        <v>0.4761907155780346</v>
       </c>
       <c r="AI2">
-        <v>1.100000023812017</v>
+        <v>1.100000023812018</v>
       </c>
       <c r="AJ2">
-        <v>0.6816683458299561</v>
+        <v>0.6816683458299555</v>
       </c>
       <c r="AK2">
-        <v>0.4761907156277814</v>
+        <v>0.4761907156277808</v>
       </c>
       <c r="AL2">
-        <v>5.555800769821566E-13</v>
+        <v>5.521992040788912E-13</v>
       </c>
       <c r="AM2">
         <v>-164.9034422584274</v>
@@ -1229,13 +1229,13 @@
         <v>158.1097491654785</v>
       </c>
       <c r="AO2">
-        <v>5.501834501217703E-13</v>
+        <v>5.607393803868089E-13</v>
       </c>
       <c r="AP2">
-        <v>-164.9034422552287</v>
+        <v>-164.9034422552288</v>
       </c>
       <c r="AQ2">
-        <v>158.1097491642544</v>
+        <v>158.1097491642543</v>
       </c>
     </row>
   </sheetData>
@@ -1420,40 +1420,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.042129368340765E-14</v>
+        <v>-2.084258736681509E-14</v>
       </c>
       <c r="O2">
-        <v>-7.307611028380883E-10</v>
+        <v>-7.307775317804774E-10</v>
       </c>
       <c r="P2">
-        <v>-2.039317060541501E-09</v>
+        <v>-2.039304539874329E-09</v>
       </c>
       <c r="Q2">
-        <v>5.210646841703876E-15</v>
+        <v>5.210646841703825E-15</v>
       </c>
       <c r="R2">
-        <v>7.307633797281129E-10</v>
+        <v>7.307868848411925E-10</v>
       </c>
       <c r="S2">
-        <v>2.039318742809639E-09</v>
+        <v>2.039294485959123E-09</v>
       </c>
       <c r="T2">
-        <v>1.042129368340745E-14</v>
+        <v>-2.016390590899383E-28</v>
       </c>
       <c r="U2">
-        <v>5.822516354120731E-09</v>
+        <v>5.822515266763499E-09</v>
       </c>
       <c r="V2">
-        <v>-3.556059113865144E-09</v>
+        <v>-3.556088454323506E-09</v>
       </c>
       <c r="W2">
-        <v>-1.04212936834075E-14</v>
+        <v>-5.210646841703724E-15</v>
       </c>
       <c r="X2">
-        <v>-5.822512395212678E-09</v>
+        <v>-5.822512743466894E-09</v>
       </c>
       <c r="Y2">
-        <v>3.556063300305623E-09</v>
+        <v>3.556087632497115E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1480,34 +1480,34 @@
         <v>0.6816683458635713</v>
       </c>
       <c r="AH2">
-        <v>0.4761907155780343</v>
+        <v>0.4761907155780348</v>
       </c>
       <c r="AI2">
         <v>1.100000023812017</v>
       </c>
       <c r="AJ2">
-        <v>0.6816683458299556</v>
+        <v>0.6816683458299557</v>
       </c>
       <c r="AK2">
-        <v>0.4761907156277811</v>
+        <v>0.4761907156277815</v>
       </c>
       <c r="AL2">
-        <v>5.561854218344969E-13</v>
+        <v>5.543010024387108E-13</v>
       </c>
       <c r="AM2">
-        <v>-164.9034422584275</v>
+        <v>-164.9034422584274</v>
       </c>
       <c r="AN2">
         <v>158.1097491654785</v>
       </c>
       <c r="AO2">
-        <v>5.664284327450757E-13</v>
+        <v>5.581691202013289E-13</v>
       </c>
       <c r="AP2">
-        <v>-164.9034422552288</v>
+        <v>-164.9034422552287</v>
       </c>
       <c r="AQ2">
-        <v>158.1097491642544</v>
+        <v>158.1097491642543</v>
       </c>
     </row>
   </sheetData>
@@ -1692,40 +1692,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-7.105427357603599E-15</v>
+        <v>-2.368475785867791E-15</v>
       </c>
       <c r="O2">
-        <v>8.289562939825719E-15</v>
+        <v>-8.289767557340117E-15</v>
       </c>
       <c r="P2">
-        <v>-1.028800051606121E-19</v>
+        <v>-1.028821204227616E-19</v>
       </c>
       <c r="Q2">
-        <v>4.736951571735755E-15</v>
+        <v>2.368475785867731E-15</v>
       </c>
       <c r="R2">
-        <v>-2.367693945555047E-15</v>
+        <v>8.290447092889443E-15</v>
       </c>
       <c r="S2">
-        <v>2.36925820815667E-15</v>
+        <v>2.369258212606294E-15</v>
       </c>
       <c r="T2">
-        <v>4.736951571735606E-15</v>
+        <v>-4.736951571735723E-15</v>
       </c>
       <c r="U2">
-        <v>4.763139806754659E-09</v>
+        <v>4.763142175230446E-09</v>
       </c>
       <c r="V2">
         <v>-4.76314691567277E-09</v>
       </c>
       <c r="W2">
-        <v>-4.736951571735632E-15</v>
+        <v>9.473903143471421E-15</v>
       </c>
       <c r="X2">
-        <v>-4.763142174828874E-09</v>
+        <v>-4.763151648732015E-09</v>
       </c>
       <c r="Y2">
-        <v>4.763137442171191E-09</v>
+        <v>4.763151653025914E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1749,37 +1749,37 @@
         <v>1.000000000000357</v>
       </c>
       <c r="AG2">
-        <v>0.4999999998169617</v>
+        <v>0.4999999998169619</v>
       </c>
       <c r="AH2">
         <v>0.5000000001833956</v>
       </c>
       <c r="AI2">
-        <v>1.000000000000357</v>
+        <v>1.000000000000358</v>
       </c>
       <c r="AJ2">
-        <v>0.4999999997748079</v>
+        <v>0.4999999997748081</v>
       </c>
       <c r="AK2">
-        <v>0.5000000002255494</v>
+        <v>0.5000000002255495</v>
       </c>
       <c r="AL2">
-        <v>7.011344205525981E-13</v>
+        <v>6.890338837962756E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999987621</v>
+        <v>-179.999999998762</v>
       </c>
       <c r="AN2">
-        <v>179.9999999987552</v>
+        <v>179.9999999987551</v>
       </c>
       <c r="AO2">
-        <v>7.332910884655591E-13</v>
+        <v>7.049230108977153E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.999999990588</v>
+        <v>-179.9999999905879</v>
       </c>
       <c r="AQ2">
-        <v>179.999999990581</v>
+        <v>179.9999999905809</v>
       </c>
     </row>
   </sheetData>
@@ -1964,40 +1964,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-7.105427357603599E-15</v>
+        <v>-2.368475785867791E-15</v>
       </c>
       <c r="O2">
-        <v>8.289562939825719E-15</v>
+        <v>-8.289767557340117E-15</v>
       </c>
       <c r="P2">
-        <v>-1.028800051606121E-19</v>
+        <v>-1.028821204227616E-19</v>
       </c>
       <c r="Q2">
-        <v>4.736951571735755E-15</v>
+        <v>2.368475785867731E-15</v>
       </c>
       <c r="R2">
-        <v>-2.367693945555047E-15</v>
+        <v>8.290447092889443E-15</v>
       </c>
       <c r="S2">
-        <v>2.36925820815667E-15</v>
+        <v>2.369258212606294E-15</v>
       </c>
       <c r="T2">
-        <v>4.736951571735606E-15</v>
+        <v>-4.736951571735723E-15</v>
       </c>
       <c r="U2">
-        <v>4.763139806754659E-09</v>
+        <v>4.763142175230446E-09</v>
       </c>
       <c r="V2">
         <v>-4.76314691567277E-09</v>
       </c>
       <c r="W2">
-        <v>-4.736951571735632E-15</v>
+        <v>9.473903143471421E-15</v>
       </c>
       <c r="X2">
-        <v>-4.763142174828874E-09</v>
+        <v>-4.763151648732015E-09</v>
       </c>
       <c r="Y2">
-        <v>4.763137442171191E-09</v>
+        <v>4.763151653025914E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2021,37 +2021,37 @@
         <v>1.000000000000357</v>
       </c>
       <c r="AG2">
-        <v>0.4999999998169617</v>
+        <v>0.4999999998169619</v>
       </c>
       <c r="AH2">
         <v>0.5000000001833956</v>
       </c>
       <c r="AI2">
-        <v>1.000000000000357</v>
+        <v>1.000000000000358</v>
       </c>
       <c r="AJ2">
-        <v>0.4999999997748079</v>
+        <v>0.4999999997748081</v>
       </c>
       <c r="AK2">
-        <v>0.5000000002255494</v>
+        <v>0.5000000002255495</v>
       </c>
       <c r="AL2">
-        <v>7.011344205525981E-13</v>
+        <v>6.890338837962756E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999987621</v>
+        <v>-179.999999998762</v>
       </c>
       <c r="AN2">
-        <v>179.9999999987552</v>
+        <v>179.9999999987551</v>
       </c>
       <c r="AO2">
-        <v>7.332910884655591E-13</v>
+        <v>7.049230108977153E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.999999990588</v>
+        <v>-179.9999999905879</v>
       </c>
       <c r="AQ2">
-        <v>179.999999990581</v>
+        <v>179.9999999905809</v>
       </c>
     </row>
   </sheetData>
@@ -2236,40 +2236,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-4.736951571761554E-15</v>
+        <v>-4.736951571761459E-15</v>
       </c>
       <c r="O2">
-        <v>-5.559741170305135E-10</v>
+        <v>-5.559687954590456E-10</v>
       </c>
       <c r="P2">
-        <v>-1.551466659908855E-09</v>
+        <v>-1.551460265200627E-09</v>
       </c>
       <c r="Q2">
-        <v>2.368475785880867E-15</v>
+        <v>4.736951571761484E-15</v>
       </c>
       <c r="R2">
-        <v>5.559730600295006E-10</v>
+        <v>5.559719683810268E-10</v>
       </c>
       <c r="S2">
-        <v>1.551469964587355E-09</v>
+        <v>1.551460265680368E-09</v>
       </c>
       <c r="T2">
-        <v>7.105427357642174E-15</v>
+        <v>-2.368475785880789E-15</v>
       </c>
       <c r="U2">
-        <v>4.833166310647397E-09</v>
+        <v>4.833180944539223E-09</v>
       </c>
       <c r="V2">
-        <v>-3.108908553939752E-09</v>
+        <v>-3.108915162337267E-09</v>
       </c>
       <c r="W2">
-        <v>-1.184237892940368E-14</v>
+        <v>4.827642713281114E-29</v>
       </c>
       <c r="X2">
-        <v>-4.833168050053326E-09</v>
+        <v>-4.833175725187439E-09</v>
       </c>
       <c r="Y2">
-        <v>3.108911751577368E-09</v>
+        <v>3.108915162620765E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2290,25 +2290,25 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.000000000005801</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AG2">
-        <v>0.6078088903891383</v>
+        <v>0.6078088903891384</v>
       </c>
       <c r="AH2">
-        <v>0.43408701041406</v>
+        <v>0.4340870104140602</v>
       </c>
       <c r="AI2">
-        <v>1.000000000005801</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AJ2">
-        <v>0.6078088903608012</v>
+        <v>0.6078088903608009</v>
       </c>
       <c r="AK2">
-        <v>0.4340870104725149</v>
+        <v>0.4340870104725145</v>
       </c>
       <c r="AL2">
-        <v>5.859035705597472E-13</v>
+        <v>5.766015366901183E-13</v>
       </c>
       <c r="AM2">
         <v>-166.2935793302449</v>
@@ -2317,7 +2317,7 @@
         <v>160.6235536346806</v>
       </c>
       <c r="AO2">
-        <v>6.099580165917517E-13</v>
+        <v>5.83927338664398E-13</v>
       </c>
       <c r="AP2">
         <v>-166.2935793242505</v>
@@ -2508,40 +2508,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-4.736951571761554E-15</v>
+        <v>-4.736951571761459E-15</v>
       </c>
       <c r="O2">
-        <v>-5.559741170305135E-10</v>
+        <v>-5.559687954590456E-10</v>
       </c>
       <c r="P2">
-        <v>-1.551466659908855E-09</v>
+        <v>-1.551460265200627E-09</v>
       </c>
       <c r="Q2">
-        <v>2.368475785880867E-15</v>
+        <v>4.736951571761484E-15</v>
       </c>
       <c r="R2">
-        <v>5.559730600295006E-10</v>
+        <v>5.559719683810268E-10</v>
       </c>
       <c r="S2">
-        <v>1.551469964587355E-09</v>
+        <v>1.551460265680368E-09</v>
       </c>
       <c r="T2">
-        <v>7.105427357642174E-15</v>
+        <v>-2.368475785880789E-15</v>
       </c>
       <c r="U2">
-        <v>4.833166310647397E-09</v>
+        <v>4.833180944539223E-09</v>
       </c>
       <c r="V2">
-        <v>-3.108908553939752E-09</v>
+        <v>-3.108915162337267E-09</v>
       </c>
       <c r="W2">
-        <v>-1.184237892940368E-14</v>
+        <v>4.827642713281114E-29</v>
       </c>
       <c r="X2">
-        <v>-4.833168050053326E-09</v>
+        <v>-4.833175725187439E-09</v>
       </c>
       <c r="Y2">
-        <v>3.108911751577368E-09</v>
+        <v>3.108915162620765E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2562,25 +2562,25 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.000000000005801</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AG2">
-        <v>0.6078088903891383</v>
+        <v>0.6078088903891384</v>
       </c>
       <c r="AH2">
-        <v>0.43408701041406</v>
+        <v>0.4340870104140602</v>
       </c>
       <c r="AI2">
-        <v>1.000000000005801</v>
+        <v>1.000000000005802</v>
       </c>
       <c r="AJ2">
-        <v>0.6078088903608012</v>
+        <v>0.6078088903608009</v>
       </c>
       <c r="AK2">
-        <v>0.4340870104725149</v>
+        <v>0.4340870104725145</v>
       </c>
       <c r="AL2">
-        <v>5.859035705597472E-13</v>
+        <v>5.766015366901183E-13</v>
       </c>
       <c r="AM2">
         <v>-166.2935793302449</v>
@@ -2589,7 +2589,7 @@
         <v>160.6235536346806</v>
       </c>
       <c r="AO2">
-        <v>6.099580165917517E-13</v>
+        <v>5.83927338664398E-13</v>
       </c>
       <c r="AP2">
         <v>-166.2935793242505</v>
@@ -2783,40 +2783,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957775481614318E-09</v>
+        <v>-2.957777652717168E-09</v>
       </c>
       <c r="O2">
-        <v>-7.394499645197981E-10</v>
+        <v>-7.394541747886307E-10</v>
       </c>
       <c r="P2">
-        <v>-7.394418546193883E-10</v>
+        <v>-7.394356051845729E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957774613426954E-09</v>
+        <v>2.957777218750374E-09</v>
       </c>
       <c r="R2">
-        <v>7.39449747472957E-10</v>
+        <v>7.394546090726451E-10</v>
       </c>
       <c r="S2">
-        <v>7.394553923404385E-10</v>
+        <v>7.394392493594122E-10</v>
       </c>
       <c r="T2">
-        <v>-8.692983954949974E-16</v>
+        <v>6.94667186913189E-15</v>
       </c>
       <c r="U2">
-        <v>-3.842246091849329E-09</v>
+        <v>-3.842255810871963E-09</v>
       </c>
       <c r="V2">
-        <v>3.842276900197467E-09</v>
+        <v>3.842268743533539E-09</v>
       </c>
       <c r="W2">
-        <v>3.474909754817485E-15</v>
+        <v>-1.735737086185743E-15</v>
       </c>
       <c r="X2">
-        <v>3.84224496378318E-09</v>
+        <v>3.842258067220216E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.842274294802062E-09</v>
+        <v>-3.842263362467878E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2837,25 +2837,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.366666674654145</v>
+        <v>0.3666666746541446</v>
       </c>
       <c r="AH2">
-        <v>0.9701088351760906</v>
+        <v>0.9701088351760905</v>
       </c>
       <c r="AI2">
-        <v>0.9701088350717372</v>
+        <v>0.9701088350717373</v>
       </c>
       <c r="AJ2">
-        <v>0.3666666746856051</v>
+        <v>0.3666666746856047</v>
       </c>
       <c r="AK2">
-        <v>0.9701088351965893</v>
+        <v>0.970108835196589</v>
       </c>
       <c r="AL2">
-        <v>0.9701088350571839</v>
+        <v>0.9701088350571843</v>
       </c>
       <c r="AM2">
-        <v>1.660609436353191E-08</v>
+        <v>1.660606275539303E-08</v>
       </c>
       <c r="AN2">
         <v>-100.8933946492837</v>
@@ -2864,7 +2864,7 @@
         <v>100.8933946504709</v>
       </c>
       <c r="AP2">
-        <v>2.218381349666855E-08</v>
+        <v>2.218382998952767E-08</v>
       </c>
       <c r="AQ2">
         <v>-100.8933946499968</v>
@@ -3058,40 +3058,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957768099864627E-09</v>
+        <v>-2.957774178952608E-09</v>
       </c>
       <c r="O2">
-        <v>-7.394540044417975E-10</v>
+        <v>-7.394568652854692E-10</v>
       </c>
       <c r="P2">
-        <v>-7.39444630289643E-10</v>
+        <v>-7.394482744010391E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957770705441821E-09</v>
+        <v>2.957773310765244E-09</v>
       </c>
       <c r="R2">
-        <v>7.394504455672649E-10</v>
+        <v>7.394592535620503E-10</v>
       </c>
       <c r="S2">
-        <v>7.394536554581588E-10</v>
+        <v>7.394618121220891E-10</v>
       </c>
       <c r="T2">
-        <v>8.683554153929811E-15</v>
+        <v>-8.57253490951972E-19</v>
       </c>
       <c r="U2">
-        <v>-3.842279242075783E-09</v>
+        <v>-3.842257632927662E-09</v>
       </c>
       <c r="V2">
-        <v>3.84226700665126E-09</v>
+        <v>3.842261625657584E-09</v>
       </c>
       <c r="W2">
-        <v>-2.604178230800681E-15</v>
+        <v>2.606468614460332E-15</v>
       </c>
       <c r="X2">
-        <v>3.842272907539534E-09</v>
+        <v>3.84227004251912E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.842265269696993E-09</v>
+        <v>-3.842259020262178E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3112,25 +3112,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.3666666746541449</v>
+        <v>0.3666666746541452</v>
       </c>
       <c r="AH2">
-        <v>0.9701088351760906</v>
+        <v>0.9701088351760907</v>
       </c>
       <c r="AI2">
-        <v>0.9701088350717376</v>
+        <v>0.9701088350717375</v>
       </c>
       <c r="AJ2">
-        <v>0.3666666746856047</v>
+        <v>0.3666666746856051</v>
       </c>
       <c r="AK2">
         <v>0.9701088351965892</v>
       </c>
       <c r="AL2">
-        <v>0.9701088350571847</v>
+        <v>0.9701088350571846</v>
       </c>
       <c r="AM2">
-        <v>1.660603904928885E-08</v>
+        <v>1.660607065742773E-08</v>
       </c>
       <c r="AN2">
         <v>-100.8933946492837</v>
@@ -3139,7 +3139,7 @@
         <v>100.8933946504709</v>
       </c>
       <c r="AP2">
-        <v>2.218379868783799E-08</v>
+        <v>2.218382559286736E-08</v>
       </c>
       <c r="AQ2">
         <v>-100.8933946499968</v>
@@ -3333,40 +3333,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-3.138977734018469E-09</v>
+        <v>-3.138983661903657E-09</v>
       </c>
       <c r="O2">
-        <v>-1.3989282080977E-09</v>
+        <v>-1.398930663932698E-09</v>
       </c>
       <c r="P2">
-        <v>-1.705574442271985E-10</v>
+        <v>-1.705607937150528E-10</v>
       </c>
       <c r="Q2">
-        <v>3.138985579230752E-09</v>
+        <v>3.138990257746516E-09</v>
       </c>
       <c r="R2">
-        <v>1.398930685760871E-09</v>
+        <v>1.398928906680983E-09</v>
       </c>
       <c r="S2">
-        <v>1.705622344475303E-10</v>
+        <v>1.70558398650106E-10</v>
       </c>
       <c r="T2">
-        <v>1.418394469858368E-09</v>
+        <v>1.418398600632456E-09</v>
       </c>
       <c r="U2">
-        <v>-2.221734806154018E-09</v>
+        <v>-2.221731608169826E-09</v>
       </c>
       <c r="V2">
-        <v>2.930938584096252E-09</v>
+        <v>2.930932353203736E-09</v>
       </c>
       <c r="W2">
-        <v>-1.41838477500467E-09</v>
+        <v>-1.418395388939246E-09</v>
       </c>
       <c r="X2">
-        <v>2.221735144565777E-09</v>
+        <v>2.221733387283917E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.930937143359717E-09</v>
+        <v>-2.930933073520698E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3387,25 +3387,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6194744497695831</v>
+        <v>0.6194744497695828</v>
       </c>
       <c r="AH2">
-        <v>0.94433477094435</v>
+        <v>0.9443347709443498</v>
       </c>
       <c r="AI2">
         <v>1.05598589769414</v>
       </c>
       <c r="AJ2">
-        <v>0.6194744497792134</v>
+        <v>0.6194744497792132</v>
       </c>
       <c r="AK2">
-        <v>0.9443347709605382</v>
+        <v>0.9443347709605379</v>
       </c>
       <c r="AL2">
         <v>1.055985897682488</v>
       </c>
       <c r="AM2">
-        <v>-10.90775017850472</v>
+        <v>-10.90775017850474</v>
       </c>
       <c r="AN2">
         <v>-108.7881138042144</v>
@@ -3414,7 +3414,7 @@
         <v>106.7392371168768</v>
       </c>
       <c r="AP2">
-        <v>-10.90775017560496</v>
+        <v>-10.90775017560495</v>
       </c>
       <c r="AQ2">
         <v>-108.7881138043734</v>
@@ -3724,40 +3724,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-3.138974905127887E-09</v>
+        <v>-3.138981196955471E-09</v>
       </c>
       <c r="O2">
-        <v>-1.398924649937926E-09</v>
+        <v>-1.398921473751762E-09</v>
       </c>
       <c r="P2">
-        <v>-1.705612617982446E-10</v>
+        <v>-1.7055647160806E-10</v>
       </c>
       <c r="Q2">
-        <v>3.138977126349669E-09</v>
+        <v>3.13898216880783E-09</v>
       </c>
       <c r="R2">
-        <v>1.3989222159311E-09</v>
+        <v>1.398921539175989E-09</v>
       </c>
       <c r="S2">
-        <v>1.705689334232382E-10</v>
+        <v>1.705579123405371E-10</v>
       </c>
       <c r="T2">
-        <v>1.418401395732375E-09</v>
+        <v>1.41839588430366E-09</v>
       </c>
       <c r="U2">
-        <v>-2.221731291590297E-09</v>
+        <v>-2.221732372117046E-09</v>
       </c>
       <c r="V2">
-        <v>2.93091654193085E-09</v>
+        <v>2.930917982633181E-09</v>
       </c>
       <c r="W2">
-        <v>-1.41838986997691E-09</v>
+        <v>-1.418390841708685E-09</v>
       </c>
       <c r="X2">
-        <v>2.221738025970439E-09</v>
+        <v>2.221742981236491E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.930924681574685E-09</v>
+        <v>-2.930922772789163E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3781,22 +3781,22 @@
         <v>0.6194744497695831</v>
       </c>
       <c r="AH2">
-        <v>0.9443347709443498</v>
+        <v>0.94433477094435</v>
       </c>
       <c r="AI2">
         <v>1.05598589769414</v>
       </c>
       <c r="AJ2">
-        <v>0.619474449779213</v>
+        <v>0.6194744497792134</v>
       </c>
       <c r="AK2">
-        <v>0.944334770960538</v>
+        <v>0.9443347709605381</v>
       </c>
       <c r="AL2">
         <v>1.055985897682488</v>
       </c>
       <c r="AM2">
-        <v>-10.90775017850475</v>
+        <v>-10.90775017850474</v>
       </c>
       <c r="AN2">
         <v>-108.7881138042144</v>
@@ -3805,7 +3805,7 @@
         <v>106.7392371168768</v>
       </c>
       <c r="AP2">
-        <v>-10.90775017560498</v>
+        <v>-10.90775017560497</v>
       </c>
       <c r="AQ2">
         <v>-108.7881138043734</v>
@@ -3999,40 +3999,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.444438725491106E-09</v>
+        <v>-2.444446225664428E-09</v>
       </c>
       <c r="O2">
-        <v>-6.111119898772559E-10</v>
+        <v>-6.111117925042733E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111112816128028E-10</v>
+        <v>-6.111109642972159E-10</v>
       </c>
       <c r="Q2">
-        <v>2.44443951538572E-09</v>
+        <v>2.444447015559047E-09</v>
       </c>
       <c r="R2">
-        <v>6.11121417571806E-10</v>
+        <v>6.111115952319626E-10</v>
       </c>
       <c r="S2">
-        <v>6.11110492221548E-10</v>
+        <v>6.111101749059587E-10</v>
       </c>
       <c r="T2">
-        <v>-5.132051725643376E-15</v>
+        <v>-3.947813837598871E-15</v>
       </c>
       <c r="U2">
-        <v>-3.175425520402609E-09</v>
+        <v>-3.175424494822511E-09</v>
       </c>
       <c r="V2">
-        <v>3.175438419305653E-09</v>
+        <v>3.175425717598496E-09</v>
       </c>
       <c r="W2">
-        <v>4.342797759843908E-15</v>
+        <v>7.900840894040333E-16</v>
       </c>
       <c r="X2">
-        <v>3.175424769685362E-09</v>
+        <v>3.175423469301903E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.175434316925762E-09</v>
+        <v>-3.175421615218607E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4056,34 +4056,34 @@
         <v>0.3333333333308633</v>
       </c>
       <c r="AH2">
-        <v>0.8819171037085269</v>
+        <v>0.8819171037085272</v>
       </c>
       <c r="AI2">
-        <v>0.8819171036611017</v>
+        <v>0.8819171036611015</v>
       </c>
       <c r="AJ2">
-        <v>0.3333333333857751</v>
+        <v>0.3333333333857756</v>
       </c>
       <c r="AK2">
-        <v>0.8819171037296488</v>
+        <v>0.8819171037296486</v>
       </c>
       <c r="AL2">
-        <v>0.8819171036503575</v>
+        <v>0.8819171036503576</v>
       </c>
       <c r="AM2">
-        <v>8.301934956203264E-09</v>
+        <v>8.302023872057068E-09</v>
       </c>
       <c r="AN2">
-        <v>-100.8933946487909</v>
+        <v>-100.8933946487908</v>
       </c>
       <c r="AO2">
         <v>100.8933946493849</v>
       </c>
       <c r="AP2">
-        <v>1.387958065703195E-08</v>
+        <v>1.387974713790135E-08</v>
       </c>
       <c r="AQ2">
-        <v>-100.8933946503433</v>
+        <v>-100.8933946503432</v>
       </c>
       <c r="AR2">
         <v>100.8933946513357</v>
@@ -4274,40 +4274,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.444438725491106E-09</v>
+        <v>-2.444446225664428E-09</v>
       </c>
       <c r="O2">
-        <v>-6.111119898772559E-10</v>
+        <v>-6.111117925042733E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111112816128028E-10</v>
+        <v>-6.111109642972159E-10</v>
       </c>
       <c r="Q2">
-        <v>2.44443951538572E-09</v>
+        <v>2.444447015559047E-09</v>
       </c>
       <c r="R2">
-        <v>6.11121417571806E-10</v>
+        <v>6.111115952319626E-10</v>
       </c>
       <c r="S2">
-        <v>6.11110492221548E-10</v>
+        <v>6.111101749059587E-10</v>
       </c>
       <c r="T2">
-        <v>-5.132051725643376E-15</v>
+        <v>-3.947813837598871E-15</v>
       </c>
       <c r="U2">
-        <v>-3.175425520402609E-09</v>
+        <v>-3.175424494822511E-09</v>
       </c>
       <c r="V2">
-        <v>3.175438419305653E-09</v>
+        <v>3.175425717598496E-09</v>
       </c>
       <c r="W2">
-        <v>4.342797759843908E-15</v>
+        <v>7.900840894040333E-16</v>
       </c>
       <c r="X2">
-        <v>3.175424769685362E-09</v>
+        <v>3.175423469301903E-09</v>
       </c>
       <c r="Y2">
-        <v>-3.175434316925762E-09</v>
+        <v>-3.175421615218607E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4331,34 +4331,34 @@
         <v>0.3333333333308633</v>
       </c>
       <c r="AH2">
-        <v>0.8819171037085269</v>
+        <v>0.8819171037085272</v>
       </c>
       <c r="AI2">
-        <v>0.8819171036611017</v>
+        <v>0.8819171036611015</v>
       </c>
       <c r="AJ2">
-        <v>0.3333333333857751</v>
+        <v>0.3333333333857756</v>
       </c>
       <c r="AK2">
-        <v>0.8819171037296488</v>
+        <v>0.8819171037296486</v>
       </c>
       <c r="AL2">
-        <v>0.8819171036503575</v>
+        <v>0.8819171036503576</v>
       </c>
       <c r="AM2">
-        <v>8.301934956203264E-09</v>
+        <v>8.302023872057068E-09</v>
       </c>
       <c r="AN2">
-        <v>-100.8933946487909</v>
+        <v>-100.8933946487908</v>
       </c>
       <c r="AO2">
         <v>100.8933946493849</v>
       </c>
       <c r="AP2">
-        <v>1.387958065703195E-08</v>
+        <v>1.387974713790135E-08</v>
       </c>
       <c r="AQ2">
-        <v>-100.8933946503433</v>
+        <v>-100.8933946503432</v>
       </c>
       <c r="AR2">
         <v>100.8933946513357</v>
@@ -4549,40 +4549,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.624749519766269E-09</v>
+        <v>-2.624767599707235E-09</v>
       </c>
       <c r="O2">
-        <v>-1.140206066457998E-09</v>
+        <v>-1.140196077607628E-09</v>
       </c>
       <c r="P2">
-        <v>-1.721730022651316E-10</v>
+        <v>-1.721745430937791E-10</v>
       </c>
       <c r="Q2">
-        <v>2.624751111137422E-09</v>
+        <v>2.624771653588768E-09</v>
       </c>
       <c r="R2">
-        <v>1.140204155094071E-09</v>
+        <v>1.140197171628709E-09</v>
       </c>
       <c r="S2">
-        <v>1.72174088066232E-10</v>
+        <v>1.721762595647642E-10</v>
       </c>
       <c r="T2">
-        <v>1.117779870941247E-09</v>
+        <v>1.117781033070002E-09</v>
       </c>
       <c r="U2">
-        <v>-1.947068357004146E-09</v>
+        <v>-1.947073756510382E-09</v>
       </c>
       <c r="V2">
-        <v>2.505960376776792E-09</v>
+        <v>2.505957574608373E-09</v>
       </c>
       <c r="W2">
-        <v>-1.117781808508442E-09</v>
+        <v>-1.117783767325475E-09</v>
       </c>
       <c r="X2">
-        <v>1.947065776136923E-09</v>
+        <v>1.947078741263146E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.505960061411218E-09</v>
+        <v>-2.505959430741333E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4606,22 +4606,22 @@
         <v>0.5421614591499193</v>
       </c>
       <c r="AH2">
-        <v>0.8576025463155461</v>
+        <v>0.8576025463155462</v>
       </c>
       <c r="AI2">
-        <v>0.9547184906659628</v>
+        <v>0.9547184906659627</v>
       </c>
       <c r="AJ2">
-        <v>0.5421614591770476</v>
+        <v>0.5421614591770481</v>
       </c>
       <c r="AK2">
-        <v>0.8576025463355481</v>
+        <v>0.857602546335548</v>
       </c>
       <c r="AL2">
         <v>0.9547184906556982</v>
       </c>
       <c r="AM2">
-        <v>-10.80277169403305</v>
+        <v>-10.80277169403301</v>
       </c>
       <c r="AN2">
         <v>-108.0887396155923</v>
@@ -4630,7 +4630,7 @@
         <v>106.1949204558219</v>
       </c>
       <c r="AP2">
-        <v>-10.80277169013764</v>
+        <v>-10.80277169013755</v>
       </c>
       <c r="AQ2">
         <v>-108.0887396163351</v>
@@ -4824,40 +4824,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.624749519766269E-09</v>
+        <v>-2.624767599707235E-09</v>
       </c>
       <c r="O2">
-        <v>-1.140206066457998E-09</v>
+        <v>-1.140196077607628E-09</v>
       </c>
       <c r="P2">
-        <v>-1.721730022651316E-10</v>
+        <v>-1.721745430937791E-10</v>
       </c>
       <c r="Q2">
-        <v>2.624751111137422E-09</v>
+        <v>2.624771653588768E-09</v>
       </c>
       <c r="R2">
-        <v>1.140204155094071E-09</v>
+        <v>1.140197171628709E-09</v>
       </c>
       <c r="S2">
-        <v>1.72174088066232E-10</v>
+        <v>1.721762595647642E-10</v>
       </c>
       <c r="T2">
-        <v>1.117779870941247E-09</v>
+        <v>1.117781033070002E-09</v>
       </c>
       <c r="U2">
-        <v>-1.947068357004146E-09</v>
+        <v>-1.947073756510382E-09</v>
       </c>
       <c r="V2">
-        <v>2.505960376776792E-09</v>
+        <v>2.505957574608373E-09</v>
       </c>
       <c r="W2">
-        <v>-1.117781808508442E-09</v>
+        <v>-1.117783767325475E-09</v>
       </c>
       <c r="X2">
-        <v>1.947065776136923E-09</v>
+        <v>1.947078741263146E-09</v>
       </c>
       <c r="Y2">
-        <v>-2.505960061411218E-09</v>
+        <v>-2.505959430741333E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4881,22 +4881,22 @@
         <v>0.5421614591499193</v>
       </c>
       <c r="AH2">
-        <v>0.8576025463155461</v>
+        <v>0.8576025463155462</v>
       </c>
       <c r="AI2">
-        <v>0.9547184906659628</v>
+        <v>0.9547184906659627</v>
       </c>
       <c r="AJ2">
-        <v>0.5421614591770476</v>
+        <v>0.5421614591770481</v>
       </c>
       <c r="AK2">
-        <v>0.8576025463355481</v>
+        <v>0.857602546335548</v>
       </c>
       <c r="AL2">
         <v>0.9547184906556982</v>
       </c>
       <c r="AM2">
-        <v>-10.80277169403305</v>
+        <v>-10.80277169403301</v>
       </c>
       <c r="AN2">
         <v>-108.0887396155923</v>
@@ -4905,7 +4905,7 @@
         <v>106.1949204558219</v>
       </c>
       <c r="AP2">
-        <v>-10.80277169013764</v>
+        <v>-10.80277169013755</v>
       </c>
       <c r="AQ2">
         <v>-108.0887396163351</v>
@@ -5099,40 +5099,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957795889522992E-09</v>
+        <v>-2.957799363287552E-09</v>
       </c>
       <c r="O2">
-        <v>-7.394602617683465E-10</v>
+        <v>-7.394255241227533E-10</v>
       </c>
       <c r="P2">
-        <v>-7.394602624166156E-10</v>
+        <v>-7.394359460646738E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957788942057315E-09</v>
+        <v>2.957788942057316E-09</v>
       </c>
       <c r="R2">
-        <v>7.394619990947401E-10</v>
+        <v>7.394342089782572E-10</v>
       </c>
       <c r="S2">
-        <v>7.394463678024705E-10</v>
+        <v>7.394359465087843E-10</v>
       </c>
       <c r="T2">
-        <v>6.947452507042306E-15</v>
+        <v>3.473687946253439E-15</v>
       </c>
       <c r="U2">
-        <v>3.842264977262212E-09</v>
+        <v>3.842268451026772E-09</v>
       </c>
       <c r="V2">
-        <v>-3.842268455463295E-09</v>
+        <v>-3.842261507934165E-09</v>
       </c>
       <c r="W2">
-        <v>1.4859953162787E-19</v>
+        <v>1.486011387885879E-19</v>
       </c>
       <c r="X2">
-        <v>-3.842268450522874E-09</v>
+        <v>-3.842266713640589E-09</v>
       </c>
       <c r="Y2">
-        <v>3.842254560908938E-09</v>
+        <v>3.842254560908925E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5153,40 +5153,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7333333491947058</v>
+        <v>0.7333333491947056</v>
       </c>
       <c r="AH2">
         <v>0.3666666743874887</v>
       </c>
       <c r="AI2">
-        <v>0.3666666748072247</v>
+        <v>0.3666666748072245</v>
       </c>
       <c r="AJ2">
-        <v>0.7333333492104359</v>
+        <v>0.7333333492104364</v>
       </c>
       <c r="AK2">
-        <v>0.3666666743489848</v>
+        <v>0.3666666743489836</v>
       </c>
       <c r="AL2">
-        <v>0.3666666748614591</v>
+        <v>0.3666666748614579</v>
       </c>
       <c r="AM2">
-        <v>1.484119334839289E-09</v>
+        <v>1.484112091307458E-09</v>
       </c>
       <c r="AN2">
-        <v>-179.9999999988592</v>
+        <v>-179.9999999988593</v>
       </c>
       <c r="AO2">
         <v>-179.9999999981704</v>
       </c>
       <c r="AP2">
-        <v>2.878544131000546E-09</v>
+        <v>2.878575263555281E-09</v>
       </c>
       <c r="AQ2">
-        <v>-179.9999999910787</v>
+        <v>-179.9999999910789</v>
       </c>
       <c r="AR2">
-        <v>179.9999999968235</v>
+        <v>179.9999999968234</v>
       </c>
     </row>
   </sheetData>
@@ -5374,40 +5374,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.957785468229308E-09</v>
+        <v>-2.957802837052114E-09</v>
       </c>
       <c r="O2">
-        <v>-7.394237872404754E-10</v>
+        <v>-7.3945852488607E-10</v>
       </c>
       <c r="P2">
-        <v>-7.394567886520498E-10</v>
+        <v>-7.394463673583651E-10</v>
       </c>
       <c r="Q2">
-        <v>2.957781994528191E-09</v>
+        <v>2.957799363350998E-09</v>
       </c>
       <c r="R2">
-        <v>7.394185770377456E-10</v>
+        <v>7.394394196251068E-10</v>
       </c>
       <c r="S2">
-        <v>7.394602628607239E-10</v>
+        <v>7.394498415670392E-10</v>
       </c>
       <c r="T2">
-        <v>1.736874619008878E-14</v>
+        <v>1.042121706790117E-14</v>
       </c>
       <c r="U2">
-        <v>3.842264977262215E-09</v>
+        <v>3.84226324037993E-09</v>
       </c>
       <c r="V2">
-        <v>-3.842261507934165E-09</v>
+        <v>-3.842261507934171E-09</v>
       </c>
       <c r="W2">
-        <v>-1.38949096434068E-14</v>
+        <v>6.947677723126577E-15</v>
       </c>
       <c r="X2">
-        <v>-3.842264976758321E-09</v>
+        <v>-3.842263239876037E-09</v>
       </c>
       <c r="Y2">
-        <v>3.842261508438059E-09</v>
+        <v>3.842261508438064E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5428,25 +5428,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7333333491947056</v>
+        <v>0.7333333491947058</v>
       </c>
       <c r="AH2">
-        <v>0.3666666743874889</v>
+        <v>0.3666666743874886</v>
       </c>
       <c r="AI2">
-        <v>0.3666666748072244</v>
+        <v>0.3666666748072249</v>
       </c>
       <c r="AJ2">
-        <v>0.7333333492104357</v>
+        <v>0.7333333492104361</v>
       </c>
       <c r="AK2">
         <v>0.3666666743489844</v>
       </c>
       <c r="AL2">
-        <v>0.3666666748614585</v>
+        <v>0.3666666748614592</v>
       </c>
       <c r="AM2">
-        <v>1.484127895376908E-09</v>
+        <v>1.484119993342182E-09</v>
       </c>
       <c r="AN2">
         <v>-179.9999999988592</v>
@@ -5455,13 +5455,13 @@
         <v>-179.9999999981704</v>
       </c>
       <c r="AP2">
-        <v>2.878582872309547E-09</v>
+        <v>2.878559176774621E-09</v>
       </c>
       <c r="AQ2">
-        <v>-179.9999999910788</v>
+        <v>-179.9999999910787</v>
       </c>
       <c r="AR2">
-        <v>179.9999999968235</v>
+        <v>179.9999999968234</v>
       </c>
     </row>
   </sheetData>
@@ -5649,40 +5649,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.272190212925716E-09</v>
+        <v>-2.272209054866225E-09</v>
       </c>
       <c r="O2">
-        <v>-1.904164080616519E-09</v>
+        <v>-1.904144870259971E-09</v>
       </c>
       <c r="P2">
-        <v>-3.132510283275749E-09</v>
+        <v>-3.132512886653956E-09</v>
       </c>
       <c r="Q2">
-        <v>2.27218616693011E-09</v>
+        <v>2.272201795757818E-09</v>
       </c>
       <c r="R2">
-        <v>1.904169666336695E-09</v>
+        <v>1.904150455980147E-09</v>
       </c>
       <c r="S2">
-        <v>3.132518087563918E-09</v>
+        <v>3.132504428914544E-09</v>
       </c>
       <c r="T2">
-        <v>7.091824722242773E-10</v>
+        <v>7.092040905412865E-10</v>
       </c>
       <c r="U2">
-        <v>4.349334771890314E-09</v>
+        <v>4.349344207605842E-09</v>
       </c>
       <c r="V2">
-        <v>-8.033481535052853E-10</v>
+        <v>-8.033449023112615E-10</v>
       </c>
       <c r="W2">
-        <v>-7.091821945524238E-10</v>
+        <v>-7.091913971545269E-10</v>
       </c>
       <c r="X2">
-        <v>-4.349318402466844E-09</v>
+        <v>-4.349327838182368E-09</v>
       </c>
       <c r="Y2">
-        <v>8.033517349041134E-10</v>
+        <v>8.033488015605268E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5703,25 +5703,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8561498316503076</v>
+        <v>0.8561498316503074</v>
       </c>
       <c r="AH2">
         <v>0.6454597859038529</v>
       </c>
       <c r="AI2">
-        <v>0.439636530314321</v>
+        <v>0.4396365303143212</v>
       </c>
       <c r="AJ2">
-        <v>0.8561498316569927</v>
+        <v>0.8561498316569928</v>
       </c>
       <c r="AK2">
-        <v>0.6454597858855413</v>
+        <v>0.6454597858855406</v>
       </c>
       <c r="AL2">
         <v>0.4396365303501952</v>
       </c>
       <c r="AM2">
-        <v>-3.92547381588037</v>
+        <v>-3.925473815880374</v>
       </c>
       <c r="AN2">
         <v>-153.8407182488145</v>
@@ -5730,13 +5730,13 @@
         <v>128.6858355510057</v>
       </c>
       <c r="AP2">
-        <v>-3.925473814878257</v>
+        <v>-3.92547381487824</v>
       </c>
       <c r="AQ2">
         <v>-153.840718245323</v>
       </c>
       <c r="AR2">
-        <v>128.685835554186</v>
+        <v>128.6858355541859</v>
       </c>
     </row>
   </sheetData>
@@ -5924,40 +5924,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.272190292475041E-09</v>
+        <v>-2.272197749701919E-09</v>
       </c>
       <c r="O2">
-        <v>-1.904139551049416E-09</v>
+        <v>-1.904160036738438E-09</v>
       </c>
       <c r="P2">
-        <v>-3.132512238838138E-09</v>
+        <v>-3.132515483974696E-09</v>
       </c>
       <c r="Q2">
-        <v>2.272178154427932E-09</v>
+        <v>2.272193981343963E-09</v>
       </c>
       <c r="R2">
-        <v>1.904150528607035E-09</v>
+        <v>1.904160133785313E-09</v>
       </c>
       <c r="S2">
-        <v>3.132507680108567E-09</v>
+        <v>3.132508975740207E-09</v>
       </c>
       <c r="T2">
-        <v>7.092109332233654E-10</v>
+        <v>7.091911195510814E-10</v>
       </c>
       <c r="U2">
-        <v>4.349322975310254E-09</v>
+        <v>4.349326538880365E-09</v>
       </c>
       <c r="V2">
-        <v>-8.033390477390358E-10</v>
+        <v>-8.033549858587049E-10</v>
       </c>
       <c r="W2">
-        <v>-7.092101002762114E-10</v>
+        <v>-7.091867958534753E-10</v>
       </c>
       <c r="X2">
-        <v>-4.349317583233379E-09</v>
+        <v>-4.349312865375616E-09</v>
       </c>
       <c r="Y2">
-        <v>8.03351404938734E-10</v>
+        <v>8.033631140831887E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5981,31 +5981,31 @@
         <v>0.8561498316503076</v>
       </c>
       <c r="AH2">
-        <v>0.6454597859038528</v>
+        <v>0.6454597859038529</v>
       </c>
       <c r="AI2">
-        <v>0.4396365303143212</v>
+        <v>0.4396365303143216</v>
       </c>
       <c r="AJ2">
-        <v>0.8561498316569925</v>
+        <v>0.8561498316569927</v>
       </c>
       <c r="AK2">
-        <v>0.6454597858855405</v>
+        <v>0.645459785885541</v>
       </c>
       <c r="AL2">
-        <v>0.4396365303501953</v>
+        <v>0.439636530350196</v>
       </c>
       <c r="AM2">
-        <v>-3.925473815880379</v>
+        <v>-3.925473815880381</v>
       </c>
       <c r="AN2">
-        <v>-153.8407182488146</v>
+        <v>-153.8407182488145</v>
       </c>
       <c r="AO2">
         <v>128.6858355510057</v>
       </c>
       <c r="AP2">
-        <v>-3.925473814878245</v>
+        <v>-3.925473814878249</v>
       </c>
       <c r="AQ2">
         <v>-153.840718245323</v>
@@ -6199,40 +6199,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.444443857195158E-09</v>
+        <v>-2.444451752114446E-09</v>
       </c>
       <c r="O2">
-        <v>-6.11111753591342E-10</v>
+        <v>-6.111101746074827E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111125436919988E-10</v>
+        <v>-6.111125436919974E-10</v>
       </c>
       <c r="Q2">
-        <v>2.444443857295829E-09</v>
+        <v>2.444450173231262E-09</v>
       </c>
       <c r="R2">
-        <v>6.111133332799003E-10</v>
+        <v>6.11108596328327E-10</v>
       </c>
       <c r="S2">
-        <v>6.111172813482793E-10</v>
+        <v>6.111109654128507E-10</v>
       </c>
       <c r="T2">
-        <v>3.157969270499488E-15</v>
+        <v>-9.473901587357771E-15</v>
       </c>
       <c r="U2">
-        <v>3.175423379427162E-09</v>
+        <v>3.175426537394877E-09</v>
       </c>
       <c r="V2">
-        <v>-3.17542496154857E-09</v>
+        <v>-3.175437593419437E-09</v>
       </c>
       <c r="W2">
-        <v>-6.315877492748083E-15</v>
+        <v>6.315993365729044E-15</v>
       </c>
       <c r="X2">
-        <v>-3.175426536978437E-09</v>
+        <v>-3.175424957994578E-09</v>
       </c>
       <c r="Y2">
-        <v>3.17541864602958E-09</v>
+        <v>3.175437593835877E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -6253,25 +6253,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6666666666635037</v>
+        <v>0.6666666666635039</v>
       </c>
       <c r="AH2">
-        <v>0.3333333331670287</v>
+        <v>0.3333333331670288</v>
       </c>
       <c r="AI2">
-        <v>0.3333333334964819</v>
+        <v>0.3333333334964821</v>
       </c>
       <c r="AJ2">
-        <v>0.6666666666909593</v>
+        <v>0.6666666666909603</v>
       </c>
       <c r="AK2">
-        <v>0.3333333331386032</v>
+        <v>0.3333333331386028</v>
       </c>
       <c r="AL2">
-        <v>0.3333333335523641</v>
+        <v>0.3333333335523637</v>
       </c>
       <c r="AM2">
-        <v>-3.647196595872111E-11</v>
+        <v>-3.647278925366374E-11</v>
       </c>
       <c r="AN2">
         <v>-179.9999999981412</v>
@@ -6280,7 +6280,7 @@
         <v>179.9999999980558</v>
       </c>
       <c r="AP2">
-        <v>1.357983604293976E-09</v>
+        <v>1.357981489916953E-09</v>
       </c>
       <c r="AQ2">
         <v>-179.9999999844856</v>
@@ -6393,16 +6393,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.4028253110876387</v>
+        <v>0.4028253110876384</v>
       </c>
       <c r="O2">
-        <v>0.4028253110894434</v>
+        <v>0.402825311089443</v>
       </c>
       <c r="P2">
-        <v>-25.88075857997284</v>
+        <v>-25.8807585799728</v>
       </c>
       <c r="Q2">
-        <v>-25.88075857298011</v>
+        <v>-25.88075857298006</v>
       </c>
     </row>
   </sheetData>
@@ -6590,40 +6590,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-2.444443857195158E-09</v>
+        <v>-2.444451752114446E-09</v>
       </c>
       <c r="O2">
-        <v>-6.11111753591342E-10</v>
+        <v>-6.111101746074827E-10</v>
       </c>
       <c r="P2">
-        <v>-6.111125436919988E-10</v>
+        <v>-6.111125436919974E-10</v>
       </c>
       <c r="Q2">
-        <v>2.444443857295829E-09</v>
+        <v>2.444450173231262E-09</v>
       </c>
       <c r="R2">
-        <v>6.111133332799003E-10</v>
+        <v>6.11108596328327E-10</v>
       </c>
       <c r="S2">
-        <v>6.111172813482793E-10</v>
+        <v>6.111109654128507E-10</v>
       </c>
       <c r="T2">
-        <v>3.157969270499488E-15</v>
+        <v>-9.473901587357771E-15</v>
       </c>
       <c r="U2">
-        <v>3.175423379427162E-09</v>
+        <v>3.175426537394877E-09</v>
       </c>
       <c r="V2">
-        <v>-3.17542496154857E-09</v>
+        <v>-3.175437593419437E-09</v>
       </c>
       <c r="W2">
-        <v>-6.315877492748083E-15</v>
+        <v>6.315993365729044E-15</v>
       </c>
       <c r="X2">
-        <v>-3.175426536978437E-09</v>
+        <v>-3.175424957994578E-09</v>
       </c>
       <c r="Y2">
-        <v>3.17541864602958E-09</v>
+        <v>3.175437593835877E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -6644,25 +6644,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6666666666635037</v>
+        <v>0.6666666666635039</v>
       </c>
       <c r="AH2">
-        <v>0.3333333331670287</v>
+        <v>0.3333333331670288</v>
       </c>
       <c r="AI2">
-        <v>0.3333333334964819</v>
+        <v>0.3333333334964821</v>
       </c>
       <c r="AJ2">
-        <v>0.6666666666909593</v>
+        <v>0.6666666666909603</v>
       </c>
       <c r="AK2">
-        <v>0.3333333331386032</v>
+        <v>0.3333333331386028</v>
       </c>
       <c r="AL2">
-        <v>0.3333333335523641</v>
+        <v>0.3333333335523637</v>
       </c>
       <c r="AM2">
-        <v>-3.647196595872111E-11</v>
+        <v>-3.647278925366374E-11</v>
       </c>
       <c r="AN2">
         <v>-179.9999999981412</v>
@@ -6671,7 +6671,7 @@
         <v>179.9999999980558</v>
       </c>
       <c r="AP2">
-        <v>1.357983604293976E-09</v>
+        <v>1.357981489916953E-09</v>
       </c>
       <c r="AQ2">
         <v>-179.9999999844856</v>
@@ -6865,40 +6865,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.941662748497022E-09</v>
+        <v>-1.941673572858143E-09</v>
       </c>
       <c r="O2">
-        <v>-1.538353581454868E-09</v>
+        <v>-1.538346776289345E-09</v>
       </c>
       <c r="P2">
-        <v>-2.506387637820217E-09</v>
+        <v>-2.506382284568683E-09</v>
       </c>
       <c r="Q2">
-        <v>1.941663776341077E-09</v>
+        <v>1.941676174933311E-09</v>
       </c>
       <c r="R2">
-        <v>1.538350817921897E-09</v>
+        <v>1.538350036055273E-09</v>
       </c>
       <c r="S2">
-        <v>2.506388827794506E-09</v>
+        <v>2.506384664154421E-09</v>
       </c>
       <c r="T2">
-        <v>5.589004354861706E-10</v>
+        <v>5.588883929925591E-10</v>
       </c>
       <c r="U2">
-        <v>3.623743767589819E-09</v>
+        <v>3.623733615840089E-09</v>
       </c>
       <c r="V2">
-        <v>-8.292800241476067E-10</v>
+        <v>-8.29286082205058E-10</v>
       </c>
       <c r="W2">
-        <v>-5.588986807169279E-10</v>
+        <v>-5.588903883772079E-10</v>
       </c>
       <c r="X2">
-        <v>-3.623737666865146E-09</v>
+        <v>-3.62374243272962E-09</v>
       </c>
       <c r="Y2">
-        <v>8.292786781270337E-10</v>
+        <v>8.292833899494908E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -6919,25 +6919,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7679592756099298</v>
+        <v>0.7679592756099299</v>
       </c>
       <c r="AH2">
-        <v>0.5655462792825742</v>
+        <v>0.5655462792825744</v>
       </c>
       <c r="AI2">
         <v>0.3792589156706165</v>
       </c>
       <c r="AJ2">
-        <v>0.7679592756256414</v>
+        <v>0.7679592756256424</v>
       </c>
       <c r="AK2">
-        <v>0.5655462792745896</v>
+        <v>0.565546279274589</v>
       </c>
       <c r="AL2">
-        <v>0.3792589157297781</v>
+        <v>0.3792589157297776</v>
       </c>
       <c r="AM2">
-        <v>-3.79347152561184</v>
+        <v>-3.793471525611841</v>
       </c>
       <c r="AN2">
         <v>-155.6266320097133</v>
@@ -6946,13 +6946,13 @@
         <v>131.4656840130516</v>
       </c>
       <c r="AP2">
-        <v>-3.793471524370541</v>
+        <v>-3.793471524370542</v>
       </c>
       <c r="AQ2">
         <v>-155.6266320036331</v>
       </c>
       <c r="AR2">
-        <v>131.4656840149959</v>
+        <v>131.4656840149958</v>
       </c>
     </row>
   </sheetData>
@@ -7140,40 +7140,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.941662748497022E-09</v>
+        <v>-1.941673572858143E-09</v>
       </c>
       <c r="O2">
-        <v>-1.538353581454868E-09</v>
+        <v>-1.538346776289345E-09</v>
       </c>
       <c r="P2">
-        <v>-2.506387637820217E-09</v>
+        <v>-2.506382284568683E-09</v>
       </c>
       <c r="Q2">
-        <v>1.941663776341077E-09</v>
+        <v>1.941676174933311E-09</v>
       </c>
       <c r="R2">
-        <v>1.538350817921897E-09</v>
+        <v>1.538350036055273E-09</v>
       </c>
       <c r="S2">
-        <v>2.506388827794506E-09</v>
+        <v>2.506384664154421E-09</v>
       </c>
       <c r="T2">
-        <v>5.589004354861706E-10</v>
+        <v>5.588883929925591E-10</v>
       </c>
       <c r="U2">
-        <v>3.623743767589819E-09</v>
+        <v>3.623733615840089E-09</v>
       </c>
       <c r="V2">
-        <v>-8.292800241476067E-10</v>
+        <v>-8.29286082205058E-10</v>
       </c>
       <c r="W2">
-        <v>-5.588986807169279E-10</v>
+        <v>-5.588903883772079E-10</v>
       </c>
       <c r="X2">
-        <v>-3.623737666865146E-09</v>
+        <v>-3.62374243272962E-09</v>
       </c>
       <c r="Y2">
-        <v>8.292786781270337E-10</v>
+        <v>8.292833899494908E-10</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -7194,25 +7194,25 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7679592756099298</v>
+        <v>0.7679592756099299</v>
       </c>
       <c r="AH2">
-        <v>0.5655462792825742</v>
+        <v>0.5655462792825744</v>
       </c>
       <c r="AI2">
         <v>0.3792589156706165</v>
       </c>
       <c r="AJ2">
-        <v>0.7679592756256414</v>
+        <v>0.7679592756256424</v>
       </c>
       <c r="AK2">
-        <v>0.5655462792745896</v>
+        <v>0.565546279274589</v>
       </c>
       <c r="AL2">
-        <v>0.3792589157297781</v>
+        <v>0.3792589157297776</v>
       </c>
       <c r="AM2">
-        <v>-3.79347152561184</v>
+        <v>-3.793471525611841</v>
       </c>
       <c r="AN2">
         <v>-155.6266320097133</v>
@@ -7221,13 +7221,13 @@
         <v>131.4656840130516</v>
       </c>
       <c r="AP2">
-        <v>-3.793471524370541</v>
+        <v>-3.793471524370542</v>
       </c>
       <c r="AQ2">
         <v>-155.6266320036331</v>
       </c>
       <c r="AR2">
-        <v>131.4656840149959</v>
+        <v>131.4656840149958</v>
       </c>
     </row>
   </sheetData>
@@ -7334,16 +7334,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.4028253110876379</v>
+        <v>0.4028253110876387</v>
       </c>
       <c r="O2">
-        <v>0.4028253110894423</v>
+        <v>0.4028253110894434</v>
       </c>
       <c r="P2">
-        <v>-25.88075857997293</v>
+        <v>-25.88075857997276</v>
       </c>
       <c r="Q2">
-        <v>-25.8807585729802</v>
+        <v>-25.88075857298002</v>
       </c>
     </row>
   </sheetData>
@@ -7682,16 +7682,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.3354590830466709</v>
+        <v>0.3354590830466711</v>
       </c>
       <c r="O2">
-        <v>0.3354590830702971</v>
+        <v>0.3354590830702975</v>
       </c>
       <c r="P2">
-        <v>-27.02488376071828</v>
+        <v>-27.02488376071815</v>
       </c>
       <c r="Q2">
-        <v>-27.02488374970901</v>
+        <v>-27.02488374970884</v>
       </c>
     </row>
   </sheetData>
@@ -7798,16 +7798,16 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.3354590830466709</v>
+        <v>0.3354590830466711</v>
       </c>
       <c r="O2">
-        <v>0.3354590830702971</v>
+        <v>0.3354590830702975</v>
       </c>
       <c r="P2">
-        <v>-27.02488376071828</v>
+        <v>-27.02488376071815</v>
       </c>
       <c r="Q2">
-        <v>-27.02488374970901</v>
+        <v>-27.02488374970884</v>
       </c>
     </row>
   </sheetData>
@@ -7992,40 +7992,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.563194052506487E-14</v>
+        <v>-1.04212936833768E-14</v>
       </c>
       <c r="O2">
-        <v>-1.302666094200621E-14</v>
+        <v>1.823722009915964E-14</v>
       </c>
       <c r="P2">
-        <v>-1.042133822648306E-14</v>
+        <v>1.042124914555161E-14</v>
       </c>
       <c r="Q2">
-        <v>-2.424819220015377E-28</v>
+        <v>5.210646841688435E-15</v>
       </c>
       <c r="R2">
-        <v>2.084305945171721E-14</v>
+        <v>-1.042082159262981E-14</v>
       </c>
       <c r="S2">
-        <v>5.211119633444434E-15</v>
+        <v>-5.210174050348486E-15</v>
       </c>
       <c r="T2">
-        <v>-2.084258736675367E-14</v>
+        <v>5.210646841688248E-15</v>
       </c>
       <c r="U2">
         <v>5.763405283190286E-09</v>
       </c>
       <c r="V2">
-        <v>-5.763402682029849E-09</v>
+        <v>-5.763392260736157E-09</v>
       </c>
       <c r="W2">
-        <v>2.084258736675349E-14</v>
+        <v>-5.210646841688312E-15</v>
       </c>
       <c r="X2">
-        <v>-5.763400072057545E-09</v>
+        <v>-5.763400072057541E-09</v>
       </c>
       <c r="Y2">
-        <v>5.763407893162592E-09</v>
+        <v>5.763402682515737E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -8046,37 +8046,37 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.100000023808766</v>
+        <v>1.100000023808765</v>
       </c>
       <c r="AG2">
-        <v>0.5500000117057466</v>
+        <v>0.5500000117057467</v>
       </c>
       <c r="AH2">
-        <v>0.550000012103019</v>
+        <v>0.5500000121030186</v>
       </c>
       <c r="AI2">
         <v>1.100000023808766</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000116593775</v>
+        <v>0.5500000116593768</v>
       </c>
       <c r="AK2">
-        <v>0.5500000121493882</v>
+        <v>0.5500000121493872</v>
       </c>
       <c r="AL2">
-        <v>6.711563520090028E-13</v>
+        <v>6.692180953301192E-13</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999995568</v>
+        <v>-179.9999999995569</v>
       </c>
       <c r="AN2">
         <v>179.9999999995499</v>
       </c>
       <c r="AO2">
-        <v>6.665770661980928E-13</v>
+        <v>6.82319240729983E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999952995</v>
+        <v>-179.9999999952996</v>
       </c>
       <c r="AQ2">
         <v>179.9999999952925</v>
